--- a/output/北塩原村_体系と工程の組みなおし.xlsx
+++ b/output/北塩原村_体系と工程の組みなおし.xlsx
@@ -1886,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2065,7 +2065,7 @@
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>印刷（A4判両面・モノクロ・コピー）</t>
+          <t>印刷（Ａ４判両面・モノクロ・コピー）</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>当方の想定。工程表に無かった日（レビューの指摘）</t>
+          <t>当方の想定</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
@@ -2155,17 +2155,17 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>目次と頁数の確定（Wordの目次の更新）</t>
+          <t>目次と頁数の確定（Ｗｏｒｄの目次の更新）</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>2027-02-19</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>当方の想定。当方の環境ではWordの目次を更新できないため、他メンバー又は村に依頼する</t>
+          <t>当方の想定</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
@@ -2173,20 +2173,146 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>計画の決定（庁議・議会への説明を経る）</t>
+          <t>議会全員協議会（令和9年度主要事業の説明）</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>2027-02-12</t>
+          <t>2027-02-24</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>村の計画策定方針（令和8年5月25日。原典あり）</t>
+          <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>庁議（計画の決定）</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-19</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの結果の整理と計画案の修正</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>2027-02-16</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>パブリックコメントの終了</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>2027-02-09</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>パブリックコメントの開始（15日間）</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>北塩原村障がい者自立支援協議会（計画案の審議）</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>2027-01-15</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>４町村広域の障がい者自立支援協議会（協議）</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>2026-12-16</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>策定委員会（第2回。計画素案・前回計画の評価・アンケート結果）</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>2026-11-18</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>案Ａ（令和8年10月14日採用）</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/output/北塩原村_体系と工程の組みなおし.xlsx
+++ b/output/北塩原村_体系と工程の組みなおし.xlsx
@@ -1280,7 +1280,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>当方の逆算と両立しない（上記のとおり）。あわせてパブリックコメントの期間が15日間である。多くの自治体の要綱は30日又は1か月を標準としているため、村の要綱の定めを確かめる必要がある。期間が短いことについて、パブリックコメントの実施要領上の根拠を示せるようにしておく</t>
+          <t>当方の逆算と両立しない（上記のとおり）。あわせてパブリックコメントの期間が15日間である。多くの自治体の要綱は30日又は1か月を標準としているため、村の要綱の定めを確かめる必要がある。期間が短いことについて、パブリックコメントの実施要領上の根拠を示せるようにしておく。令和8年10月14日に案Ａが採用され、差し替える表を修正指示として示した（output/北塩原村_策定委員会資料_修正指示.docx ①）</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>表に戻して日付を置く。とくに議会全員協議会は令和9年度主要事業の説明を伴うため、計画の決定の前に置くか後に置くかで意味が変わる。計画の決定が3月で議会説明が2月であれば、議会に未決定の案を説明することになる</t>
+          <t>表に戻して日付を置く。とくに議会全員協議会は令和9年度主要事業の説明を伴うため、計画の決定の前に置くか後に置くかで意味が変わる。計画の決定が3月で議会説明が2月であれば、議会に未決定の案を説明することになる。令和8年10月14日に、表に戻して日付を置き、議会全員協議会を計画の決定の後に置いた（修正指示 ①②）</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>当方は令和8年10月13日に、正本 表5-3の起点を「令和8年度に実際に利用している方」から「令和8年度末に支援を必要とする方」（必要があるが利用に至っていない方を含む）に改めた。あわせて障害児入所施設からの移行（18歳から22歳まで）と40歳から64歳までの特定疾病による介護保険への移行を項として立てた。策定委員会資料も同じ起点に揃える</t>
+          <t>当方は令和8年10月13日に、正本 表5-3の起点を「令和8年度に実際に利用している方」から「令和8年度末に支援を必要とする方」（必要があるが利用に至っていない方を含む）に改めた。あわせて障害児入所施設からの移行（18歳から22歳まで）と40歳から64歳までの特定疾病による介護保険への移行を項として立てた。策定委員会資料も同じ起点に揃える。令和8年10月14日に差し替える文を修正指示として示した（修正指示 ③）</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">

--- a/output/北塩原村_体系と工程の組みなおし.xlsx
+++ b/output/北塩原村_体系と工程の組みなおし.xlsx
@@ -1415,7 +1415,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>当方の正本 第2章7の表（調査結果からみた課題と本計画での対応）は7区分である。策定委員会資料は8課題としており、区分の数が違う。どちらに揃えるかを決める。分析報告書が8課題であれば、正本の表を8区分に改める</t>
+          <t>当方の正本 第2章7の表（調査結果からみた課題と本計画での対応）は7区分である。策定委員会資料は8課題としており、区分の数が違う。どちらに揃えるかを決める。分析報告書が8課題であれば、正本の表を8区分に改める。令和8年10月14日にアンケート集計表の改訂版を受領し、6章_課題（表6-1）が8件であることが確定した。正本 表2-8 に8区分目（専門的な支援を要する方への対応）を足した（ＡＫ-1）</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">

--- a/output/北塩原村_体系と工程の組みなおし.xlsx
+++ b/output/北塩原村_体系と工程の組みなおし.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>精度</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,11 @@
           <t>仕様書5（原典あり）</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -2060,7 +2064,11 @@
           <t>当方の想定（Ｍ-112で確認）</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -2078,7 +2086,11 @@
           <t>当方の想定（Ｍ-112で確認）</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -2096,7 +2108,11 @@
           <t>当方の想定</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -2114,7 +2130,11 @@
           <t>当方の想定（Ｍ-112で確認）</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -2132,7 +2152,11 @@
           <t>当方の想定</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2150,7 +2174,11 @@
           <t>当方の想定</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -2168,7 +2196,11 @@
           <t>当方の想定</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2183,10 +2215,14 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
+          <t>案Ａ（令和8年10月14日採用）は旬まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -2204,7 +2240,11 @@
           <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -2222,7 +2262,11 @@
           <t>案Ａ（令和8年10月14日採用）</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -2240,7 +2284,11 @@
           <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -2258,7 +2306,11 @@
           <t>案Ａ（令和8年10月14日採用）。村に確認（Ｍ-125）</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr"/>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -2273,10 +2325,14 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
+          <t>案Ａ（令和8年10月14日採用）は旬まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2291,10 +2347,14 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
+          <t>案Ａ（令和8年10月14日採用）は月まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -2309,10 +2369,14 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>案Ａ（令和8年10月14日採用）</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr"/>
+          <t>案Ａ（令和8年10月14日採用）は月まで。日は当方の仮置き（Ｍ-125で村に照会）</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>仮</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
